--- a/notification_configs/09_late_submission_alerts.xlsx
+++ b/notification_configs/09_late_submission_alerts.xlsx
@@ -125,8 +125,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LateSubmissionAlerts" displayName="LateSubmissionAlerts" ref="A1:W14" headerRowCount="1">
-  <autoFilter ref="A1:W14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LateSubmissionAlerts" displayName="LateSubmissionAlerts" ref="A1:W7" headerRowCount="1">
+  <autoFilter ref="A1:W7"/>
   <tableColumns count="23">
     <tableColumn id="1" name="Primary_Key"/>
     <tableColumn id="2" name="Contact_Email"/>
@@ -445,16 +445,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W14"/>
+  <dimension ref="A1:W7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="29" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
@@ -462,7 +462,7 @@
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="50" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="21" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
@@ -593,27 +593,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LATE_OT1_20250910</t>
+          <t>LATE_01111_20250911</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ot1@vendor.com</t>
+          <t>thunderblunder018@gmail.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Gopal</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>OT1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+          <t>01111</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>MTK34710</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Chandresh</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>chandresh.kerkar1@gmail.com</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>LATE_SUBMISSION</t>
@@ -644,12 +656,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>🚨 URGENT: Daily attendance submission missing - Test</t>
+          <t>🚨 URGENT: Daily attendance submission missing - Gopal</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>general_alerts</t>
+          <t>alerts_mtk34710</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -669,12 +681,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>03:41:16</t>
+          <t>02:47:34</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -684,34 +696,46 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2025-09-10 03:41:16</t>
+          <t>2025-09-11 02:47:34</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LATE_OT2_20250910</t>
+          <t>LATE_EMP001_20250911</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ot2@vendor.com</t>
+          <t>john.vendor@company.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>abc2</t>
+          <t>John Smith</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>OT2</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>EMP001</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>M001</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Alice Johnson</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>alice.manager@attendo.com</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>LATE_SUBMISSION</t>
@@ -742,12 +766,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>🚨 URGENT: Daily attendance submission missing - abc2</t>
+          <t>🚨 URGENT: Daily attendance submission missing - John Smith</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>general_alerts</t>
+          <t>alerts_m001</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -767,12 +791,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>03:41:16</t>
+          <t>02:47:34</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -782,34 +806,46 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2025-09-10 03:41:16</t>
+          <t>2025-09-11 02:47:34</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LATE_OT3_20250910</t>
+          <t>LATE_EMP002_20250911</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ot3@vendor.com</t>
+          <t>jane.vendor@company.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>abc3</t>
+          <t>Jane Wilson</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>OT3</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>EMP002</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>M001</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Alice Johnson</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>alice.manager@attendo.com</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>LATE_SUBMISSION</t>
@@ -840,12 +876,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>🚨 URGENT: Daily attendance submission missing - abc3</t>
+          <t>🚨 URGENT: Daily attendance submission missing - Jane Wilson</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>general_alerts</t>
+          <t>alerts_m001</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -865,12 +901,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>03:41:16</t>
+          <t>02:47:34</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -880,44 +916,44 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2025-09-10 03:41:16</t>
+          <t>2025-09-11 02:47:34</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LATE_V001_20250910</t>
+          <t>LATE_EMP003_20250911</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>chandresh.kerkar1@gmail.com</t>
+          <t>mike.vendor@company.com</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chandresh Kerkar</t>
+          <t>Mike Rodriguez</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>V001</t>
+          <t>EMP003</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>M001</t>
+          <t>M002</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sarah Johnson</t>
+          <t>Bob Chen</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>sarah.johnson@attendo.com</t>
+          <t>bob.manager@attendo.com</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -950,12 +986,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>🚨 URGENT: Daily attendance submission missing - Chandresh Kerkar</t>
+          <t>🚨 URGENT: Daily attendance submission missing - Mike Rodriguez</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>alerts_m001</t>
+          <t>alerts_m002</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -975,12 +1011,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>03:41:16</t>
+          <t>02:47:34</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -990,44 +1026,44 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2025-09-10 03:41:16</t>
+          <t>2025-09-11 02:47:34</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LATE_VND002_20250910</t>
+          <t>LATE_EMP004_20250911</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>jane.smith@vendor1.com</t>
+          <t>sarah.vendor@company.com</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jane Smith</t>
+          <t>Sarah Parker</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VND002</t>
+          <t>EMP004</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>M001</t>
+          <t>M003</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sarah Johnson</t>
+          <t>Carol Davis</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>sarah.johnson@attendo.com</t>
+          <t>carol.manager@attendo.com</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1060,12 +1096,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>🚨 URGENT: Daily attendance submission missing - Jane Smith</t>
+          <t>🚨 URGENT: Daily attendance submission missing - Sarah Parker</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>alerts_m001</t>
+          <t>alerts_m003</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1085,12 +1121,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>03:41:16</t>
+          <t>02:47:34</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1100,29 +1136,29 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2025-09-10 03:41:16</t>
+          <t>2025-09-11 02:47:34</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LATE_VND003_20250910</t>
+          <t>LATE_EMP005_20250911</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>robert.wilson@vendor2.com</t>
+          <t>david.vendor@company.com</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Robert Wilson</t>
+          <t>David Kim</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VND003</t>
+          <t>EMP005</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1132,12 +1168,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sarah Johnson</t>
+          <t>Alice Johnson</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>sarah.johnson@attendo.com</t>
+          <t>alice.manager@attendo.com</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1170,7 +1206,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>🚨 URGENT: Daily attendance submission missing - Robert Wilson</t>
+          <t>🚨 URGENT: Daily attendance submission missing - David Kim</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1195,12 +1231,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>03:41:16</t>
+          <t>02:47:34</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1210,777 +1246,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2025-09-10 03:41:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>LATE_VND004_20250910</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>lisa.brown@vendor2.com</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Lisa Brown</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>VND004</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>M002</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Michael Chen</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>michael.chen@attendo.com</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>LATE_SUBMISSION</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>24</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>🚨 URGENT: Daily attendance submission missing - Lisa Brown</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>alerts_m002</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>EMAIL,TEAMS,SMS</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>03:41:16</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>2025-09-10 03:41:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>LATE_VND005_20250910</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>david.lee@vendor3.com</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>David Lee</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>VND005</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>M002</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Michael Chen</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>michael.chen@attendo.com</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>LATE_SUBMISSION</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>24</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>🚨 URGENT: Daily attendance submission missing - David Lee</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>alerts_m002</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>EMAIL,TEAMS,SMS</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>03:41:16</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>2025-09-10 03:41:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>LATE_VND006_20250910</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>maria.garcia@vendor3.com</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Maria Garcia</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>VND006</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>M002</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Michael Chen</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>michael.chen@attendo.com</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>LATE_SUBMISSION</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>24</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>🚨 URGENT: Daily attendance submission missing - Maria Garcia</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>alerts_m002</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>EMAIL,TEAMS,SMS</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>03:41:16</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>2025-09-10 03:41:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>LATE_VND007_20250910</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>james.miller@vendor4.com</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>James Miller</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>VND007</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>M003</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Emily Davis</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>emily.davis@attendo.com</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>LATE_SUBMISSION</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>24</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>🚨 URGENT: Daily attendance submission missing - James Miller</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>alerts_m003</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>EMAIL,TEAMS,SMS</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>03:41:16</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>2025-09-10 03:41:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>LATE_VND008_20250910</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>anna.taylor@vendor4.com</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Anna Taylor</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>VND008</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>M003</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Emily Davis</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>emily.davis@attendo.com</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>LATE_SUBMISSION</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>24</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>🚨 URGENT: Daily attendance submission missing - Anna Taylor</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>alerts_m003</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>EMAIL,TEAMS,SMS</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>03:41:16</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>2025-09-10 03:41:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>LATE_VND009_20250910</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>chris.anderson@vendor5.com</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Chris Anderson</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>VND009</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>M003</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Emily Davis</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>emily.davis@attendo.com</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>LATE_SUBMISSION</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>24</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>🚨 URGENT: Daily attendance submission missing - Chris Anderson</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>alerts_m003</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>EMAIL,TEAMS,SMS</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>03:41:16</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>2025-09-10 03:41:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>LATE_VND010_20250910</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>sophie.martin@vendor5.com</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Sophie Martin</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>VND010</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>M001</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Sarah Johnson</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>sarah.johnson@attendo.com</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>LATE_SUBMISSION</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>24</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>🚨 URGENT: Daily attendance submission missing - Sophie Martin</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>alerts_m001</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>EMAIL,TEAMS,SMS</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>03:41:16</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>2025-09-10 03:41:16</t>
+          <t>2025-09-11 02:47:34</t>
         </is>
       </c>
     </row>

--- a/notification_configs/09_late_submission_alerts.xlsx
+++ b/notification_configs/09_late_submission_alerts.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>02:47:34</t>
+          <t>10:17:41</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2025-09-11 02:47:34</t>
+          <t>2025-09-11 10:17:41</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>02:47:34</t>
+          <t>10:17:41</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2025-09-11 02:47:34</t>
+          <t>2025-09-11 10:17:41</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>02:47:34</t>
+          <t>10:17:41</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2025-09-11 02:47:34</t>
+          <t>2025-09-11 10:17:41</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>02:47:34</t>
+          <t>10:17:41</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2025-09-11 02:47:34</t>
+          <t>2025-09-11 10:17:41</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>02:47:34</t>
+          <t>10:17:41</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2025-09-11 02:47:34</t>
+          <t>2025-09-11 10:17:41</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>02:47:34</t>
+          <t>10:17:41</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2025-09-11 02:47:34</t>
+          <t>2025-09-11 10:17:41</t>
         </is>
       </c>
     </row>

--- a/notification_configs/09_late_submission_alerts.xlsx
+++ b/notification_configs/09_late_submission_alerts.xlsx
@@ -125,8 +125,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LateSubmissionAlerts" displayName="LateSubmissionAlerts" ref="A1:W7" headerRowCount="1">
-  <autoFilter ref="A1:W7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LateSubmissionAlerts" displayName="LateSubmissionAlerts" ref="A1:W10" headerRowCount="1">
+  <autoFilter ref="A1:W10"/>
   <tableColumns count="23">
     <tableColumn id="1" name="Primary_Key"/>
     <tableColumn id="2" name="Contact_Email"/>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>10:17:41</t>
+          <t>19:08:12</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2025-09-11 10:17:41</t>
+          <t>2025-09-11 19:08:12</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>10:17:41</t>
+          <t>19:08:12</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2025-09-11 10:17:41</t>
+          <t>2025-09-11 19:08:12</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>10:17:41</t>
+          <t>19:08:12</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2025-09-11 10:17:41</t>
+          <t>2025-09-11 19:08:12</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>10:17:41</t>
+          <t>19:08:12</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2025-09-11 10:17:41</t>
+          <t>2025-09-11 19:08:12</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>10:17:41</t>
+          <t>19:08:12</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2025-09-11 10:17:41</t>
+          <t>2025-09-11 19:08:12</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>10:17:41</t>
+          <t>19:08:12</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1246,7 +1246,301 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2025-09-11 10:17:41</t>
+          <t>2025-09-11 19:08:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LATE_OT1_20250911</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ot1@vendor.com</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>abc1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>OT1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>LATE_SUBMISSION</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>24</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>🚨 URGENT: Daily attendance submission missing - abc1</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>general_alerts</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>EMAIL,TEAMS,SMS</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>19:08:12</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2025-09-11 19:08:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LATE_OT2_20250911</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ot2@vendor.com</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>abc2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>OT2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>LATE_SUBMISSION</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>24</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>🚨 URGENT: Daily attendance submission missing - abc2</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>general_alerts</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>EMAIL,TEAMS,SMS</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>19:08:12</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2025-09-11 19:08:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LATE_OT3_20250911</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ot3@vendor.com</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>abc3</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>OT3</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>LATE_SUBMISSION</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>24</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>🚨 URGENT: Daily attendance submission missing - abc3</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>general_alerts</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>EMAIL,TEAMS,SMS</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>19:08:12</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2025-09-11 19:08:12</t>
         </is>
       </c>
     </row>

--- a/notification_configs/09_late_submission_alerts.xlsx
+++ b/notification_configs/09_late_submission_alerts.xlsx
@@ -125,8 +125,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LateSubmissionAlerts" displayName="LateSubmissionAlerts" ref="A1:W10" headerRowCount="1">
-  <autoFilter ref="A1:W10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="LateSubmissionAlerts" displayName="LateSubmissionAlerts" ref="A1:W6" headerRowCount="1">
+  <autoFilter ref="A1:W6"/>
   <tableColumns count="23">
     <tableColumn id="1" name="Primary_Key"/>
     <tableColumn id="2" name="Contact_Email"/>
@@ -445,16 +445,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W10"/>
+  <dimension ref="A1:W6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
@@ -462,7 +462,7 @@
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="50" customWidth="1" min="14" max="14"/>
-    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="21" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
@@ -593,37 +593,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LATE_01111_20250911</t>
+          <t>LATE_EMP001_20250911</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>thunderblunder018@gmail.com</t>
+          <t>john.vendor@company.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Gopal</t>
+          <t>John Smith</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>01111</t>
+          <t>EMP001</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MTK34710</t>
+          <t>M001</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chandresh</t>
+          <t>Alice Johnson</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>chandresh.kerkar1@gmail.com</t>
+          <t>alice.manager@attendo.com</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -656,12 +656,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>🚨 URGENT: Daily attendance submission missing - Gopal</t>
+          <t>🚨 URGENT: Daily attendance submission missing - John Smith</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>alerts_mtk34710</t>
+          <t>alerts_m001</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>19:08:12</t>
+          <t>22:16:31</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -696,29 +696,29 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2025-09-11 19:08:12</t>
+          <t>2025-09-11 22:16:31</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LATE_EMP001_20250911</t>
+          <t>LATE_EMP002_20250911</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>john.vendor@company.com</t>
+          <t>jane.vendor@company.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Jane Wilson</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EMP001</t>
+          <t>EMP002</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>🚨 URGENT: Daily attendance submission missing - John Smith</t>
+          <t>🚨 URGENT: Daily attendance submission missing - Jane Wilson</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>19:08:12</t>
+          <t>22:16:31</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -806,44 +806,44 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2025-09-11 19:08:12</t>
+          <t>2025-09-11 22:16:31</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LATE_EMP002_20250911</t>
+          <t>LATE_EMP003_20250911</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jane.vendor@company.com</t>
+          <t>mike.vendor@company.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jane Wilson</t>
+          <t>Mike Rodriguez</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EMP002</t>
+          <t>EMP003</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>M001</t>
+          <t>M002</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Alice Johnson</t>
+          <t>Bob Chen</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>alice.manager@attendo.com</t>
+          <t>bob.manager@attendo.com</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>🚨 URGENT: Daily attendance submission missing - Jane Wilson</t>
+          <t>🚨 URGENT: Daily attendance submission missing - Mike Rodriguez</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>alerts_m001</t>
+          <t>alerts_m002</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>19:08:12</t>
+          <t>22:16:31</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -916,44 +916,44 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2025-09-11 19:08:12</t>
+          <t>2025-09-11 22:16:31</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LATE_EMP003_20250911</t>
+          <t>LATE_EMP004_20250911</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mike.vendor@company.com</t>
+          <t>sarah.vendor@company.com</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mike Rodriguez</t>
+          <t>Sarah Parker</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EMP003</t>
+          <t>EMP004</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>M002</t>
+          <t>M003</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bob Chen</t>
+          <t>Carol Davis</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>bob.manager@attendo.com</t>
+          <t>carol.manager@attendo.com</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>🚨 URGENT: Daily attendance submission missing - Mike Rodriguez</t>
+          <t>🚨 URGENT: Daily attendance submission missing - Sarah Parker</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>alerts_m002</t>
+          <t>alerts_m003</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19:08:12</t>
+          <t>22:16:31</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1026,44 +1026,44 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2025-09-11 19:08:12</t>
+          <t>2025-09-11 22:16:31</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LATE_EMP004_20250911</t>
+          <t>LATE_EMP005_20250911</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sarah.vendor@company.com</t>
+          <t>david.vendor@company.com</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sarah Parker</t>
+          <t>David Kim</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EMP004</t>
+          <t>EMP005</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>M003</t>
+          <t>M001</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Carol Davis</t>
+          <t>Alice Johnson</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>carol.manager@attendo.com</t>
+          <t>alice.manager@attendo.com</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>🚨 URGENT: Daily attendance submission missing - Sarah Parker</t>
+          <t>🚨 URGENT: Daily attendance submission missing - David Kim</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>alerts_m003</t>
+          <t>alerts_m001</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>19:08:12</t>
+          <t>22:16:31</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1136,411 +1136,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2025-09-11 19:08:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>LATE_EMP005_20250911</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>david.vendor@company.com</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>David Kim</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>EMP005</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>M001</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Alice Johnson</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>alice.manager@attendo.com</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>LATE_SUBMISSION</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>24</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>🚨 URGENT: Daily attendance submission missing - David Kim</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>alerts_m001</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>EMAIL,TEAMS,SMS</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>19:08:12</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>2025-09-11 19:08:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>LATE_OT1_20250911</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ot1@vendor.com</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>abc1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>OT1</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>LATE_SUBMISSION</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>24</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>🚨 URGENT: Daily attendance submission missing - abc1</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>general_alerts</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>EMAIL,TEAMS,SMS</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>19:08:12</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>2025-09-11 19:08:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>LATE_OT2_20250911</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ot2@vendor.com</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>abc2</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>OT2</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>LATE_SUBMISSION</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>24</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>🚨 URGENT: Daily attendance submission missing - abc2</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>general_alerts</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>EMAIL,TEAMS,SMS</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>19:08:12</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>2025-09-11 19:08:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>LATE_OT3_20250911</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ot3@vendor.com</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>abc3</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>OT3</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>LATE_SUBMISSION</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>24</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>🚨 URGENT: Daily attendance submission missing - abc3</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>general_alerts</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>EMAIL,TEAMS,SMS</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>19:08:12</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>2025-09-11 19:08:12</t>
+          <t>2025-09-11 22:16:31</t>
         </is>
       </c>
     </row>
